--- a/06_Office_Related/01_NSO_work/06_SL_to_PIVOT_to_Compare_with_WP/02_GJ_WP_2026-27/SL 2.0/BHAVNAGAR.xlsx
+++ b/06_Office_Related/01_NSO_work/06_SL_to_PIVOT_to_Compare_with_WP/02_GJ_WP_2026-27/SL 2.0/BHAVNAGAR.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2059F1F-9FA7-4C8B-A86F-AE6746243846}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C7FA3DF-EB1A-480A-BBD4-A0B78704A924}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="450" windowWidth="13575" windowHeight="15255" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CENTRAL 2.0" sheetId="1" r:id="rId1"/>
@@ -576,10 +576,30 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -594,29 +614,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -899,115 +899,115 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.28515625" customWidth="1"/>
-    <col min="2" max="2" width="11.140625" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" style="10" customWidth="1"/>
+    <col min="1" max="1" width="12.33203125" customWidth="1"/>
+    <col min="2" max="2" width="11.109375" customWidth="1"/>
+    <col min="3" max="3" width="13.6640625" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:12" ht="18" x14ac:dyDescent="0.3">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-    </row>
-    <row r="2" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+    </row>
+    <row r="2" spans="1:12" ht="18" x14ac:dyDescent="0.3">
+      <c r="A2" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
-      <c r="L2" s="17"/>
-    </row>
-    <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="18"/>
-      <c r="K3" s="18"/>
-      <c r="L3" s="18"/>
-    </row>
-    <row r="4" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
+    </row>
+    <row r="3" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
+      <c r="J3" s="20"/>
+      <c r="K3" s="20"/>
+      <c r="L3" s="20"/>
+    </row>
+    <row r="4" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="20"/>
+      <c r="B4" s="28"/>
       <c r="C4" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="D4" s="23">
+      <c r="D4" s="25">
         <v>14</v>
       </c>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23">
+      <c r="E4" s="25"/>
+      <c r="F4" s="25">
         <v>16</v>
       </c>
-      <c r="G4" s="23"/>
-      <c r="H4" s="23">
+      <c r="G4" s="25"/>
+      <c r="H4" s="25">
         <v>18</v>
       </c>
-      <c r="I4" s="23"/>
-      <c r="J4" s="23">
+      <c r="I4" s="25"/>
+      <c r="J4" s="25">
         <v>16</v>
       </c>
-      <c r="K4" s="23"/>
+      <c r="K4" s="25"/>
       <c r="L4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="22.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="21"/>
-      <c r="B5" s="22"/>
+    <row r="5" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="29"/>
+      <c r="B5" s="30"/>
       <c r="C5" s="12"/>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="E5" s="27"/>
-      <c r="F5" s="27" t="s">
+      <c r="E5" s="24"/>
+      <c r="F5" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="27"/>
-      <c r="H5" s="27" t="s">
+      <c r="G5" s="24"/>
+      <c r="H5" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="I5" s="27"/>
-      <c r="J5" s="27" t="s">
+      <c r="I5" s="24"/>
+      <c r="J5" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="K5" s="27"/>
+      <c r="K5" s="24"/>
       <c r="L5" s="1">
         <f>D4+F4+H4+J4</f>
         <v>64</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>27</v>
       </c>
@@ -1045,7 +1045,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A7" s="16" t="s">
         <v>9</v>
       </c>
@@ -1080,7 +1080,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>11</v>
       </c>
@@ -1111,7 +1111,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>11</v>
       </c>
@@ -1142,7 +1142,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>11</v>
       </c>
@@ -1173,7 +1173,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>15</v>
       </c>
@@ -1208,7 +1208,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
         <v>17</v>
       </c>
@@ -1239,7 +1239,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
         <v>17</v>
       </c>
@@ -1274,7 +1274,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
         <v>20</v>
       </c>
@@ -1305,7 +1305,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>20</v>
       </c>
@@ -1332,7 +1332,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A16" s="16" t="s">
         <v>20</v>
       </c>
@@ -1359,7 +1359,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A17" s="16" t="s">
         <v>24</v>
       </c>
@@ -1390,7 +1390,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A18" s="16" t="s">
         <v>24</v>
       </c>
@@ -1421,12 +1421,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="23" t="s">
+    <row r="19" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="B19" s="23"/>
-      <c r="C19" s="23"/>
+      <c r="B19" s="25"/>
+      <c r="C19" s="25"/>
       <c r="D19" s="4">
         <f>SUM(D7:D18)</f>
         <v>14</v>
@@ -1452,27 +1452,27 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="18" t="s">
+    <row r="20" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="B20" s="18"/>
-      <c r="C20" s="18"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="18"/>
-      <c r="I20" s="18"/>
-      <c r="J20" s="18"/>
-      <c r="K20" s="18"/>
-      <c r="L20" s="18"/>
-    </row>
-    <row r="21" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="20"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="20"/>
+      <c r="I20" s="20"/>
+      <c r="J20" s="20"/>
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+    </row>
+    <row r="21" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A21" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="B21" s="29" t="s">
+      <c r="B21" s="17" t="s">
         <v>78</v>
       </c>
       <c r="C21" s="9" t="s">
@@ -1495,7 +1495,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A22" s="15" t="s">
         <v>35</v>
       </c>
@@ -1522,11 +1522,11 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A23" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="B23" s="29" t="s">
+      <c r="B23" s="17" t="s">
         <v>76</v>
       </c>
       <c r="C23" s="9" t="s">
@@ -1549,11 +1549,11 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A24" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="B24" s="29" t="s">
+      <c r="B24" s="17" t="s">
         <v>15</v>
       </c>
       <c r="C24" s="9" t="s">
@@ -1576,7 +1576,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A25" s="15" t="s">
         <v>20</v>
       </c>
@@ -1603,7 +1603,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A26" s="15" t="s">
         <v>20</v>
       </c>
@@ -1630,7 +1630,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A27" s="15" t="s">
         <v>41</v>
       </c>
@@ -1657,12 +1657,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="24" t="s">
+    <row r="28" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A28" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="B28" s="25"/>
-      <c r="C28" s="26"/>
+      <c r="B28" s="22"/>
+      <c r="C28" s="23"/>
       <c r="D28" s="4">
         <f>SUM(D21:D27)</f>
         <v>0</v>
@@ -1688,12 +1688,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="24" t="s">
+    <row r="29" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A29" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="B29" s="25"/>
-      <c r="C29" s="26"/>
+      <c r="B29" s="22"/>
+      <c r="C29" s="23"/>
       <c r="D29" s="4">
         <f>+D19+D28</f>
         <v>14</v>
@@ -1719,24 +1719,32 @@
         <v>64</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="30" t="s">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A30" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="B30" s="30"/>
-      <c r="C30" s="30"/>
-      <c r="D30" s="30"/>
-      <c r="E30" s="30"/>
-      <c r="F30" s="30"/>
-      <c r="G30" s="30"/>
-      <c r="H30" s="30"/>
-      <c r="I30" s="30"/>
-      <c r="J30" s="30"/>
-      <c r="K30" s="30"/>
-      <c r="L30" s="30"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="19"/>
+      <c r="J30" s="19"/>
+      <c r="K30" s="19"/>
+      <c r="L30" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A4:B5"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="J4:K4"/>
     <mergeCell ref="A30:L30"/>
     <mergeCell ref="A20:L20"/>
     <mergeCell ref="A28:C28"/>
@@ -1746,14 +1754,6 @@
     <mergeCell ref="H5:I5"/>
     <mergeCell ref="J5:K5"/>
     <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A4:B5"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="J4:K4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1762,115 +1762,115 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="28" t="s">
+    <row r="1" spans="1:12" ht="18" x14ac:dyDescent="0.3">
+      <c r="A1" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
-    </row>
-    <row r="2" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
+    </row>
+    <row r="2" spans="1:12" ht="18" x14ac:dyDescent="0.3">
+      <c r="A2" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
-      <c r="L2" s="17"/>
-    </row>
-    <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="18"/>
-      <c r="K3" s="18"/>
-      <c r="L3" s="18"/>
-    </row>
-    <row r="4" spans="1:12" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
+    </row>
+    <row r="3" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
+      <c r="J3" s="20"/>
+      <c r="K3" s="20"/>
+      <c r="L3" s="20"/>
+    </row>
+    <row r="4" spans="1:12" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="20"/>
+      <c r="B4" s="28"/>
       <c r="C4" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="D4" s="23">
+      <c r="D4" s="25">
         <v>8</v>
       </c>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23">
+      <c r="E4" s="25"/>
+      <c r="F4" s="25">
         <v>8</v>
       </c>
-      <c r="G4" s="23"/>
-      <c r="H4" s="23">
+      <c r="G4" s="25"/>
+      <c r="H4" s="25">
         <v>10</v>
       </c>
-      <c r="I4" s="23"/>
-      <c r="J4" s="23">
+      <c r="I4" s="25"/>
+      <c r="J4" s="25">
         <v>10</v>
       </c>
-      <c r="K4" s="23"/>
+      <c r="K4" s="25"/>
       <c r="L4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="22.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="21"/>
-      <c r="B5" s="22"/>
+    <row r="5" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="29"/>
+      <c r="B5" s="30"/>
       <c r="C5" s="12"/>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="E5" s="27"/>
-      <c r="F5" s="27" t="s">
+      <c r="E5" s="24"/>
+      <c r="F5" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="27"/>
-      <c r="H5" s="27" t="s">
+      <c r="G5" s="24"/>
+      <c r="H5" s="24" t="s">
         <v>82</v>
       </c>
-      <c r="I5" s="27"/>
-      <c r="J5" s="27" t="s">
+      <c r="I5" s="24"/>
+      <c r="J5" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="K5" s="27"/>
+      <c r="K5" s="24"/>
       <c r="L5" s="1">
         <f>D4+F4+H4+J4</f>
         <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>27</v>
       </c>
@@ -1908,7 +1908,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
@@ -1939,7 +1939,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>47</v>
       </c>
@@ -1966,7 +1966,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>47</v>
       </c>
@@ -2001,7 +2001,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>11</v>
       </c>
@@ -2024,7 +2024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>11</v>
       </c>
@@ -2051,7 +2051,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>15</v>
       </c>
@@ -2082,7 +2082,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>15</v>
       </c>
@@ -2109,7 +2109,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>17</v>
       </c>
@@ -2136,11 +2136,11 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="31" t="s">
+      <c r="B15" s="18" t="s">
         <v>77</v>
       </c>
       <c r="C15" s="2" t="s">
@@ -2159,11 +2159,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="31" t="s">
+      <c r="B16" s="18" t="s">
         <v>77</v>
       </c>
       <c r="C16" s="2" t="s">
@@ -2186,11 +2186,11 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="31" t="s">
+      <c r="B17" s="18" t="s">
         <v>77</v>
       </c>
       <c r="C17" s="2" t="s">
@@ -2213,7 +2213,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" ht="18" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>41</v>
       </c>
@@ -2240,12 +2240,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="23" t="s">
+    <row r="19" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="B19" s="23"/>
-      <c r="C19" s="23"/>
+      <c r="B19" s="25"/>
+      <c r="C19" s="25"/>
       <c r="D19" s="4">
         <f>SUM(D7:D18)</f>
         <v>8</v>
@@ -2271,27 +2271,27 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="18" t="s">
+    <row r="20" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="B20" s="18"/>
-      <c r="C20" s="18"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="18"/>
-      <c r="I20" s="18"/>
-      <c r="J20" s="18"/>
-      <c r="K20" s="18"/>
-      <c r="L20" s="18"/>
-    </row>
-    <row r="21" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="20"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="20"/>
+      <c r="I20" s="20"/>
+      <c r="J20" s="20"/>
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+    </row>
+    <row r="21" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B21" s="29" t="s">
+      <c r="B21" s="17" t="s">
         <v>79</v>
       </c>
       <c r="C21" s="2" t="s">
@@ -2314,11 +2314,11 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B22" s="29" t="s">
+      <c r="B22" s="17" t="s">
         <v>76</v>
       </c>
       <c r="C22" s="2" t="s">
@@ -2341,11 +2341,11 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="29" t="s">
+    <row r="23" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A23" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="B23" s="29" t="s">
+      <c r="B23" s="17" t="s">
         <v>15</v>
       </c>
       <c r="C23" s="2" t="s">
@@ -2368,7 +2368,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>17</v>
       </c>
@@ -2395,12 +2395,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="24" t="s">
+    <row r="25" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A25" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="B25" s="25"/>
-      <c r="C25" s="26"/>
+      <c r="B25" s="22"/>
+      <c r="C25" s="23"/>
       <c r="D25" s="4">
         <f>SUM(D21:D24)</f>
         <v>0</v>
@@ -2426,12 +2426,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="24" t="s">
+    <row r="26" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A26" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="B26" s="25"/>
-      <c r="C26" s="26"/>
+      <c r="B26" s="22"/>
+      <c r="C26" s="23"/>
       <c r="D26" s="4">
         <f>+D19+D25</f>
         <v>8</v>
@@ -2457,32 +2457,24 @@
         <v>36</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="30" t="s">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A27" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="B27" s="30"/>
-      <c r="C27" s="30"/>
-      <c r="D27" s="30"/>
-      <c r="E27" s="30"/>
-      <c r="F27" s="30"/>
-      <c r="G27" s="30"/>
-      <c r="H27" s="30"/>
-      <c r="I27" s="30"/>
-      <c r="J27" s="30"/>
-      <c r="K27" s="30"/>
-      <c r="L27" s="30"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="19"/>
+      <c r="K27" s="19"/>
+      <c r="L27" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A27:L27"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:L20"/>
-    <mergeCell ref="A25:C25"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A3:L3"/>
@@ -2492,6 +2484,14 @@
     <mergeCell ref="H4:I4"/>
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="D5:E5"/>
+    <mergeCell ref="A27:L27"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:L20"/>
+    <mergeCell ref="A25:C25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
